--- a/data/trans_orig/IP07_C14_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C14_2023-Habitat-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han producido situaciones de cyberbulling en su colegio en 2023 (tasa de respuesta: 94,11%)</t>
+          <t>Menores según si se han producido situaciones de cyberbulling en su colegio/instituto en 2023 (tasa de respuesta: 94,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6058</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10890</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12,92%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>23,23%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2837</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1067</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6402</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,54%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11276</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9099</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15328</t>
+          <t>15204</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>40827</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>35995</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>44251</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87,08%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>76,77%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,38%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>28336</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>24771</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30106</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>90,9%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>79,46%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>41098</t>
+          <t>31091</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36084</t>
+          <t>27677</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45185</t>
+          <t>33025</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>69434</t>
+          <t>71918</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63205</t>
+          <t>65861</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73976</t>
+          <t>76138</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,92%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>46885</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>46885</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>46885</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47360</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47360</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47360</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>78533</t>
+          <t>81065</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78533</t>
+          <t>81065</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>78533</t>
+          <t>81065</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>16911</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19374</t>
+          <t>11431</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>17845</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11532</t>
+          <t>10555</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27282</t>
+          <t>25756</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>90998</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>83829</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>95560</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,33%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>83,21%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,86%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>45419</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>40339</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>48589</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>86,61%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>76,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>90710</t>
+          <t>48923</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82159</t>
+          <t>44585</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95557</t>
+          <t>52376</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>136128</t>
+          <t>139921</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>126691</t>
+          <t>131000</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>142441</t>
+          <t>146201</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>93,27%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>100740</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>100740</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>100740</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>52440</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>52440</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>52440</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>101533</t>
+          <t>56016</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>101533</t>
+          <t>56016</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>101533</t>
+          <t>56016</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>153973</t>
+          <t>156756</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>153973</t>
+          <t>156756</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>153973</t>
+          <t>156756</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4167</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1316</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8681</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,01%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,69%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7259</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14485</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,32%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4259</t>
+          <t>7473</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>12522</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>11518</t>
+          <t>11640</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19923</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>47856</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>43342</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>50707</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,99%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>83,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,47%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>63062</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>55836</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>68620</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>89,68%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>79,4%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48184</t>
+          <t>39884</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43639</t>
+          <t>34835</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51005</t>
+          <t>43290</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>111247</t>
+          <t>87740</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>102842</t>
+          <t>81053</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>117598</t>
+          <t>92236</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>52023</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>52023</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>52023</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>70321</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>70321</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>70321</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>52443</t>
+          <t>47357</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52443</t>
+          <t>47357</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52443</t>
+          <t>47357</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>122765</t>
+          <t>99380</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>122765</t>
+          <t>99380</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>122765</t>
+          <t>99380</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9431</t>
+          <t>11626</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15492</t>
+          <t>17781</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12056</t>
+          <t>9635</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18468</t>
+          <t>15981</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,22 +1824,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>21487</t>
+          <t>21261</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14646</t>
+          <t>15063</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29441</t>
+          <t>28935</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>37794</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>31639</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>42717</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>76,48%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>64,02%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>86,44%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>38562</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>32501</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>42347</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>80,35%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>67,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>88,24%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>37514</t>
+          <t>41321</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31102</t>
+          <t>34975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42835</t>
+          <t>45046</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,27 +1937,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>76076</t>
+          <t>79116</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68122</t>
+          <t>71442</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>82917</t>
+          <t>85314</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>49420</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>49420</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>49420</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>47993</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>47993</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>47993</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49570</t>
+          <t>50956</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49570</t>
+          <t>50956</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49570</t>
+          <t>50956</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>97563</t>
+          <t>100377</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>97563</t>
+          <t>100377</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>97563</t>
+          <t>100377</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>31593</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>22255</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>42528</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,68%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8,94%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>17,07%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>26548</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>16535</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>36535</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13,15%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>18,09%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>33400</t>
+          <t>27291</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24269</t>
+          <t>21073</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46183</t>
+          <t>36454</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>59948</t>
+          <t>58883</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45397</t>
+          <t>46261</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73927</t>
+          <t>72535</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>217475</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>206540</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>226813</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,32%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>82,93%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>91,06%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>175379</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>165392</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>185392</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>86,85%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>81,91%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>91,81%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>217506</t>
+          <t>161219</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204723</t>
+          <t>152056</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>226637</t>
+          <t>167437</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>392885</t>
+          <t>378694</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>378906</t>
+          <t>365042</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>407436</t>
+          <t>391316</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,43%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>249068</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>249068</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>249068</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>201927</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>201927</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>201927</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>250906</t>
+          <t>188510</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>250906</t>
+          <t>188510</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>250906</t>
+          <t>188510</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>452833</t>
+          <t>437577</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>452833</t>
+          <t>437577</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>452833</t>
+          <t>437577</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
